--- a/bom/RB_SWITCH_RevD_PCBWay_BOM.xlsx
+++ b/bom/RB_SWITCH_RevD_PCBWay_BOM.xlsx
@@ -355,7 +355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A2:I25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="12" customWidth="1" style="2" min="1" max="1"/>
@@ -369,6 +369,7 @@
     <col width="90" customWidth="1" style="2" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="15" customHeight="1" s="3">
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -376,6 +377,9 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6" ht="15" customHeight="1" s="3">
       <c r="A6" s="4" t="inlineStr">
         <is>
@@ -495,7 +499,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Texas_DRC0010J_ThermalVias</t>
+          <t>Texas_DRC0010J</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -515,7 +519,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>U_CHG</t>
+          <t>U_CHG1</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -558,7 +562,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>J_USB</t>
+          <t>J_USB1</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
@@ -601,7 +605,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>J_BAT</t>
+          <t>J_BAT1</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
@@ -677,7 +681,7 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Digi-Key SRN4018-2R2MCT-ND. CHANGED from SRN4026-2R2M to match PCB footprint L_Bourns-SRN4018. Schematic still references SRN4026 footprint - reconcile.</t>
+          <t>Digi-Key SRN4018-2R2MCT-ND. CHANGED from SRN4026-2R2M to match PCB footprint L_Bourns-SRN4018. Schematic and PCB both use the L_Bourns-SRN4018 footprint.</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SW_RST</t>
+          <t>SW_RST1</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
@@ -1160,7 +1164,7 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SW_BOOT</t>
+          <t>SW_BOOT1</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
@@ -1226,7 +1230,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>SW_TH_Tactile_Omron_B3F-1000</t>
+          <t>SW_TH_Tactile_Omron_B3F-100x</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">

--- a/bom/RB_SWITCH_RevD_PCBWay_BOM.xlsx
+++ b/bom/RB_SWITCH_RevD_PCBWay_BOM.xlsx
@@ -666,7 +666,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2.2 uH shielded power inductor, 4x4x1.8 mm, Isat 3.0 A</t>
+          <t>2.2 uH shielded power inductor, 4x4 mm, 1.88 mm max height, Isat 3.0 A</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1035,11 +1035,11 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C4,C12</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Digi-Key 1276-1860-1-ND.</t>
+          <t>Digi-Key 1276-1860-1-ND. C4: charger VBUS input. C12: EN-to-GND, forms an RC reset delay with R5.</t>
         </is>
       </c>
     </row>
